--- a/data/NIKE.xlsx
+++ b/data/NIKE.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H867"/>
+  <dimension ref="A1:H956"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -35145,6 +35145,3566 @@
         </is>
       </c>
       <c r="H867" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="2" t="n">
+        <v>867</v>
+      </c>
+      <c r="B868" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C868" s="2" t="inlineStr">
+        <is>
+          <t>【470yuan】【LJR】【DN3707-100】J3 做旧白水泥</t>
+        </is>
+      </c>
+      <c r="D868" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/216704263?uid=1&amp;isSubCate=true&amp;referrercate=514308</t>
+        </is>
+      </c>
+      <c r="E868" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7428248669</t>
+        </is>
+      </c>
+      <c r="F868" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7428248669&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G868" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H868" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="2" t="n">
+        <v>868</v>
+      </c>
+      <c r="B869" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C869" s="2" t="inlineStr">
+        <is>
+          <t>【470yuan】【LJR】Air Jordan 3 Retro "Rare Air" 黑灰红 稀有空气</t>
+        </is>
+      </c>
+      <c r="D869" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/207418065?uid=1&amp;isSubCate=true&amp;referrercate=514308</t>
+        </is>
+      </c>
+      <c r="E869" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7428248669</t>
+        </is>
+      </c>
+      <c r="F869" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7428248669&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G869" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H869" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="2" t="n">
+        <v>869</v>
+      </c>
+      <c r="B870" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C870" s="2" t="inlineStr">
+        <is>
+          <t>【470Y】【LJR】 CT8532-111 白猫</t>
+        </is>
+      </c>
+      <c r="D870" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/201182629?uid=1&amp;isSubCate=true&amp;referrercate=514308</t>
+        </is>
+      </c>
+      <c r="E870" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7428248669</t>
+        </is>
+      </c>
+      <c r="F870" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7428248669&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G870" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H870" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="2" t="n">
+        <v>870</v>
+      </c>
+      <c r="B871" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C871" s="2" t="inlineStr">
+        <is>
+          <t>【470Y】【LJR】【CT8532-101】北卡蓝</t>
+        </is>
+      </c>
+      <c r="D871" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/200243616?uid=1&amp;isSubCate=true&amp;referrercate=514308</t>
+        </is>
+      </c>
+      <c r="E871" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7428248669</t>
+        </is>
+      </c>
+      <c r="F871" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7428248669&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G871" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H871" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="2" t="n">
+        <v>871</v>
+      </c>
+      <c r="B872" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C872" s="2" t="inlineStr">
+        <is>
+          <t>【470Y】【LJR】【CT8532-001】AJ3 黑猫</t>
+        </is>
+      </c>
+      <c r="D872" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064139?uid=1&amp;isSubCate=true&amp;referrercate=514308</t>
+        </is>
+      </c>
+      <c r="E872" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7428248669</t>
+        </is>
+      </c>
+      <c r="F872" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7428248669&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G872" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H872" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="2" t="n">
+        <v>872</v>
+      </c>
+      <c r="B873" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C873" s="2" t="inlineStr">
+        <is>
+          <t>【470Y】【LJR】【DN3707-010】AJ3奥利奥黑水泥</t>
+        </is>
+      </c>
+      <c r="D873" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064116?uid=1&amp;isSubCate=true&amp;referrercate=514308</t>
+        </is>
+      </c>
+      <c r="E873" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7428248669</t>
+        </is>
+      </c>
+      <c r="F873" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7428248669&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G873" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H873" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="2" t="n">
+        <v>873</v>
+      </c>
+      <c r="B874" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C874" s="2" t="inlineStr">
+        <is>
+          <t>【420yuan】【GX】【CT8532-111】AJ3白猫</t>
+        </is>
+      </c>
+      <c r="D874" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/204376714?uid=1&amp;isSubCate=true&amp;referrercate=514298</t>
+        </is>
+      </c>
+      <c r="E874" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7430603222</t>
+        </is>
+      </c>
+      <c r="F874" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7430603222&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G874" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H874" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="2" t="n">
+        <v>874</v>
+      </c>
+      <c r="B875" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C875" s="2" t="inlineStr">
+        <is>
+          <t>【420yuan】【GX】AJ3 "Rare Air"稀有空气</t>
+        </is>
+      </c>
+      <c r="D875" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/200880317?uid=1&amp;isSubCate=true&amp;referrercate=514298</t>
+        </is>
+      </c>
+      <c r="E875" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7430603222</t>
+        </is>
+      </c>
+      <c r="F875" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7430603222&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G875" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H875" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="2" t="n">
+        <v>875</v>
+      </c>
+      <c r="B876" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C876" s="2" t="inlineStr">
+        <is>
+          <t>【450Y】【GX】【HV8571-100】AJ3 AMM 联名紫 灰蓝</t>
+        </is>
+      </c>
+      <c r="D876" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/189465133?uid=1&amp;isSubCate=true&amp;referrercate=514298</t>
+        </is>
+      </c>
+      <c r="E876" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7430603222</t>
+        </is>
+      </c>
+      <c r="F876" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7430603222&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G876" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H876" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="2" t="n">
+        <v>876</v>
+      </c>
+      <c r="B877" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C877" s="2" t="inlineStr">
+        <is>
+          <t>【420Y】【GX】【DA3595-100】AJ3 藤原浩闪电</t>
+        </is>
+      </c>
+      <c r="D877" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/189465043?uid=1&amp;isSubCate=true&amp;referrercate=514298</t>
+        </is>
+      </c>
+      <c r="E877" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7430603222</t>
+        </is>
+      </c>
+      <c r="F877" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7430603222&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G877" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H877" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="2" t="n">
+        <v>877</v>
+      </c>
+      <c r="B878" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C878" s="2" t="inlineStr">
+        <is>
+          <t>【420Y】【GX】【DN3707-100】AJ3 做旧白水泥</t>
+        </is>
+      </c>
+      <c r="D878" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/189464807?uid=1&amp;isSubCate=true&amp;referrercate=514298</t>
+        </is>
+      </c>
+      <c r="E878" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7430603222</t>
+        </is>
+      </c>
+      <c r="F878" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7430603222&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G878" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H878" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="2" t="n">
+        <v>878</v>
+      </c>
+      <c r="B879" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C879" s="2" t="inlineStr">
+        <is>
+          <t>【420Y】【GX】【CT8532-001】黑猫</t>
+        </is>
+      </c>
+      <c r="D879" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064324?uid=1&amp;isSubCate=true&amp;referrercate=514298</t>
+        </is>
+      </c>
+      <c r="E879" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7430603222</t>
+        </is>
+      </c>
+      <c r="F879" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7430603222&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G879" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H879" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="2" t="n">
+        <v>879</v>
+      </c>
+      <c r="B880" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C880" s="2" t="inlineStr">
+        <is>
+          <t>【420Y】【GX】【DN3707-010】 AJ3复刻奥利奥黑水泥</t>
+        </is>
+      </c>
+      <c r="D880" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064299?uid=1&amp;isSubCate=true&amp;referrercate=514298</t>
+        </is>
+      </c>
+      <c r="E880" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7430603222</t>
+        </is>
+      </c>
+      <c r="F880" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7430603222&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G880" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H880" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="2" t="n">
+        <v>880</v>
+      </c>
+      <c r="B881" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C881" s="2" t="inlineStr">
+        <is>
+          <t>【410Y】【Y3】【CT8532-001】黑猫</t>
+        </is>
+      </c>
+      <c r="D881" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064390?uid=1&amp;isSubCate=true&amp;referrercate=514300</t>
+        </is>
+      </c>
+      <c r="E881" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7441573607</t>
+        </is>
+      </c>
+      <c r="F881" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7441573607&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G881" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H881" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="2" t="n">
+        <v>881</v>
+      </c>
+      <c r="B882" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C882" s="2" t="inlineStr">
+        <is>
+          <t>【410Y】【Y3版】【DN3707-010】 Jordan Air Jordan 3 retro cardinal red</t>
+        </is>
+      </c>
+      <c r="D882" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064352?uid=1&amp;isSubCate=true&amp;referrercate=514300</t>
+        </is>
+      </c>
+      <c r="E882" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7441573607</t>
+        </is>
+      </c>
+      <c r="F882" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7441573607&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G882" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H882" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="2" t="n">
+        <v>882</v>
+      </c>
+      <c r="B883" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C883" s="2" t="inlineStr">
+        <is>
+          <t>【390yuan】【RN】IR0912-400 李维斯蓝</t>
+        </is>
+      </c>
+      <c r="D883" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/235416082?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E883" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F883" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G883" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H883" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="2" t="n">
+        <v>883</v>
+      </c>
+      <c r="B884" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C884" s="2" t="inlineStr">
+        <is>
+          <t>【390yuan】【RN】854262-106 白蓝</t>
+        </is>
+      </c>
+      <c r="D884" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/229064532?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E884" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F884" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G884" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H884" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="2" t="n">
+        <v>884</v>
+      </c>
+      <c r="B885" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C885" s="2" t="inlineStr">
+        <is>
+          <t>【390yuan】【RN】IB1482-100 韩国限定</t>
+        </is>
+      </c>
+      <c r="D885" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/225218809?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E885" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F885" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G885" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H885" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="2" t="n">
+        <v>885</v>
+      </c>
+      <c r="B886" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C886" s="2" t="inlineStr">
+        <is>
+          <t>【390yuan】【RN】IF4491-100 迈阿密</t>
+        </is>
+      </c>
+      <c r="D886" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/225173214?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E886" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F886" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G886" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H886" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="2" t="n">
+        <v>886</v>
+      </c>
+      <c r="B887" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C887" s="2" t="inlineStr">
+        <is>
+          <t>【390yuan】【RN】HV8571-100 AMM灰蓝</t>
+        </is>
+      </c>
+      <c r="D887" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/214817093?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E887" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F887" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G887" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H887" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="2" t="n">
+        <v>887</v>
+      </c>
+      <c r="B888" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C888" s="2" t="inlineStr">
+        <is>
+          <t>【390yuan】【RN】DA3595-100 藤原浩闪电</t>
+        </is>
+      </c>
+      <c r="D888" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/214817037?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E888" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F888" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G888" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H888" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="2" t="n">
+        <v>888</v>
+      </c>
+      <c r="B889" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C889" s="2" t="inlineStr">
+        <is>
+          <t>【390yuan】【RN】FJ9479-100 象牙白</t>
+        </is>
+      </c>
+      <c r="D889" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/214816980?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E889" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F889" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G889" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H889" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="2" t="n">
+        <v>889</v>
+      </c>
+      <c r="B890" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C890" s="2" t="inlineStr">
+        <is>
+          <t>【390yuan】【RN】【CT8532-104】北卡蓝</t>
+        </is>
+      </c>
+      <c r="D890" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/214816917?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E890" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F890" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G890" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H890" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="2" t="n">
+        <v>890</v>
+      </c>
+      <c r="B891" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C891" s="2" t="inlineStr">
+        <is>
+          <t>【390yuan】【RN】DN3707-160 火焰红</t>
+        </is>
+      </c>
+      <c r="D891" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/214262999?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E891" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F891" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G891" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H891" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="2" t="n">
+        <v>891</v>
+      </c>
+      <c r="B892" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C892" s="2" t="inlineStr">
+        <is>
+          <t>【390Y】【RN】【DA3595-001】AJ3 反转藤原浩</t>
+        </is>
+      </c>
+      <c r="D892" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/194113227?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E892" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F892" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G892" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H892" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="2" t="n">
+        <v>892</v>
+      </c>
+      <c r="B893" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C893" s="2" t="inlineStr">
+        <is>
+          <t>【390Y】【RN】AJ3 白蓝【CT8532-101】</t>
+        </is>
+      </c>
+      <c r="D893" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/192750629?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E893" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F893" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G893" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H893" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="2" t="n">
+        <v>893</v>
+      </c>
+      <c r="B894" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C894" s="2" t="inlineStr">
+        <is>
+          <t>【390Y】【RN】复刻白猫 CT8532-111</t>
+        </is>
+      </c>
+      <c r="D894" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/192237796?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E894" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F894" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G894" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H894" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="2" t="n">
+        <v>894</v>
+      </c>
+      <c r="B895" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C895" s="2" t="inlineStr">
+        <is>
+          <t>【390Y】【RN】【DH3434-110】AJ3 AMM 联名白</t>
+        </is>
+      </c>
+      <c r="D895" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/191882316?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E895" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F895" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G895" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H895" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="2" t="n">
+        <v>895</v>
+      </c>
+      <c r="B896" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C896" s="2" t="inlineStr">
+        <is>
+          <t>【390Y】【RN】【DN3707-010】AJ3 黑水泥</t>
+        </is>
+      </c>
+      <c r="D896" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064466?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E896" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F896" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G896" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H896" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="2" t="n">
+        <v>896</v>
+      </c>
+      <c r="B897" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C897" s="2" t="inlineStr">
+        <is>
+          <t>【390Y】【RN】【DN3707-100】J3 做旧白水泥</t>
+        </is>
+      </c>
+      <c r="D897" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064446?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E897" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F897" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G897" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H897" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="2" t="n">
+        <v>897</v>
+      </c>
+      <c r="B898" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C898" s="2" t="inlineStr">
+        <is>
+          <t>【390Y】【RN】【FN0344-901】AJ3 白彩虹</t>
+        </is>
+      </c>
+      <c r="D898" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064439?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E898" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F898" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G898" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H898" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="B899" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C899" s="2" t="inlineStr">
+        <is>
+          <t>【390Y】【RN】【CT8532-001】AJ3 黑猫</t>
+        </is>
+      </c>
+      <c r="D899" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064275?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E899" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F899" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G899" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H899" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="2" t="n">
+        <v>899</v>
+      </c>
+      <c r="B900" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C900" s="2" t="inlineStr">
+        <is>
+          <t>【390Y】【RN】【FN0344-001】AJ3 黑彩虹</t>
+        </is>
+      </c>
+      <c r="D900" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064255?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E900" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F900" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G900" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H900" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="B901" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C901" s="2" t="inlineStr">
+        <is>
+          <t>【400yuan】【OG】 CK9246-100 米银</t>
+        </is>
+      </c>
+      <c r="D901" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/223349677?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E901" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F901" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G901" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H901" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="2" t="n">
+        <v>901</v>
+      </c>
+      <c r="B902" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C902" s="2" t="inlineStr">
+        <is>
+          <t>【400Y】【OG】【IB8967-004】AJ3 黑蓝</t>
+        </is>
+      </c>
+      <c r="D902" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/194127379?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E902" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F902" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G902" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H902" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="2" t="n">
+        <v>902</v>
+      </c>
+      <c r="B903" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C903" s="2" t="inlineStr">
+        <is>
+          <t>【450Y】【OG】【DN3707-010 】奥利奥黑水泥</t>
+        </is>
+      </c>
+      <c r="D903" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064172?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E903" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F903" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G903" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H903" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="2" t="n">
+        <v>903</v>
+      </c>
+      <c r="B904" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C904" s="2" t="inlineStr">
+        <is>
+          <t>【450Y】【OG】【FZ7974-300】Nina Chanel Abney x Air Jordan 3 Retro AJ3 乔3纽约艺术家联名</t>
+        </is>
+      </c>
+      <c r="D904" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064155?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E904" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F904" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G904" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H904" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="2" t="n">
+        <v>904</v>
+      </c>
+      <c r="B905" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C905" s="2" t="inlineStr">
+        <is>
+          <t>【440Y】【OG】 【FN0344-001】APJ Balvin x Air Jordan AJ3</t>
+        </is>
+      </c>
+      <c r="D905" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064219?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E905" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F905" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G905" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H905" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="2" t="n">
+        <v>905</v>
+      </c>
+      <c r="B906" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C906" s="2" t="inlineStr">
+        <is>
+          <t>【440Y】【OG】【FN0344-901】APJ Balvin x Air Jordan AJ3</t>
+        </is>
+      </c>
+      <c r="D906" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064202?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E906" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F906" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G906" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H906" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="2" t="n">
+        <v>906</v>
+      </c>
+      <c r="B907" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C907" s="2" t="inlineStr">
+        <is>
+          <t>【400Y】【OG】【 DN3707-100】 Jordan Air Jordan 3 White Cement Reimagined</t>
+        </is>
+      </c>
+      <c r="D907" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064624?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E907" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F907" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G907" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H907" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="2" t="n">
+        <v>907</v>
+      </c>
+      <c r="B908" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C908" s="2" t="inlineStr">
+        <is>
+          <t>【400Y】【OG】【CT8532-102】 Jordan Air Jordan 3白黑摩卡</t>
+        </is>
+      </c>
+      <c r="D908" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064610?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E908" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F908" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G908" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H908" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="2" t="n">
+        <v>908</v>
+      </c>
+      <c r="B909" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C909" s="2" t="inlineStr">
+        <is>
+          <t>【400Y】【OG】【CT8532-126】 Jordan Air Jordan 3 retro cardinal red</t>
+        </is>
+      </c>
+      <c r="D909" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064597?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E909" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F909" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G909" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H909" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="2" t="n">
+        <v>909</v>
+      </c>
+      <c r="B910" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C910" s="2" t="inlineStr">
+        <is>
+          <t>【400Y】【OG】【DA3595-100】 Fragment Design x Jordan Air Jordan 3 retro sp white</t>
+        </is>
+      </c>
+      <c r="D910" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064581?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E910" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F910" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G910" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H910" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="2" t="n">
+        <v>910</v>
+      </c>
+      <c r="B911" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C911" s="2" t="inlineStr">
+        <is>
+          <t>【400Y】【OG】【DH3434-110】4 a aniere x Jordan Air Jordan 3 retro sp mediumgrey”</t>
+        </is>
+      </c>
+      <c r="D911" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064563?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E911" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F911" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G911" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H911" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="2" t="n">
+        <v>911</v>
+      </c>
+      <c r="B912" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C912" s="2" t="inlineStr">
+        <is>
+          <t>【400Y】【OG】【FJ9479-100】AJ3 灰白爆裂</t>
+        </is>
+      </c>
+      <c r="D912" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064545?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E912" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F912" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G912" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H912" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="2" t="n">
+        <v>912</v>
+      </c>
+      <c r="B913" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C913" s="2" t="inlineStr">
+        <is>
+          <t>【400Y】【OG】【HJ0178-600】粉色</t>
+        </is>
+      </c>
+      <c r="D913" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064512?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E913" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F913" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G913" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H913" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="2" t="n">
+        <v>913</v>
+      </c>
+      <c r="B914" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C914" s="2" t="inlineStr">
+        <is>
+          <t>【 400 】 【 OG 】 【 CT8532-140 】 AJ3 Midnight Blue!</t>
+        </is>
+      </c>
+      <c r="D914" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185066068?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E914" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F914" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G914" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H914" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="2" t="n">
+        <v>914</v>
+      </c>
+      <c r="B915" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C915" s="2" t="inlineStr">
+        <is>
+          <t>【 400 】 【OG】 【 854262 001】AJ3 black cement!</t>
+        </is>
+      </c>
+      <c r="D915" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185066055?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E915" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F915" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G915" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H915" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="2" t="n">
+        <v>915</v>
+      </c>
+      <c r="B916" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C916" s="2" t="inlineStr">
+        <is>
+          <t>【 400 】 【OG】 【CK9246-001  】 Oreo Black Cement!</t>
+        </is>
+      </c>
+      <c r="D916" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185066032?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E916" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F916" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G916" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H916" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="2" t="n">
+        <v>916</v>
+      </c>
+      <c r="B917" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C917" s="2" t="inlineStr">
+        <is>
+          <t>【 400 】 【OG】 【CT8532-104】 AJ3 North Carolina Blue!</t>
+        </is>
+      </c>
+      <c r="D917" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185066017?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E917" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F917" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G917" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H917" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="2" t="n">
+        <v>917</v>
+      </c>
+      <c r="B918" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C918" s="2" t="inlineStr">
+        <is>
+          <t>【 400 】 【OG】 【CT8532-145】AJ3 Racing Blue!</t>
+        </is>
+      </c>
+      <c r="D918" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065997?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E918" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F918" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G918" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H918" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="B919" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C919" s="2" t="inlineStr">
+        <is>
+          <t>【 450 】 【 OG 】 【 FZ4811-001 】 AJ3AMM Joint Black Purple!</t>
+        </is>
+      </c>
+      <c r="D919" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065956?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E919" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F919" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G919" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H919" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="2" t="n">
+        <v>919</v>
+      </c>
+      <c r="B920" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C920" s="2" t="inlineStr">
+        <is>
+          <t>【290Y】【LJ】【 CT8532-148】奇才蓝</t>
+        </is>
+      </c>
+      <c r="D920" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065154?uid=1&amp;isSubCate=true&amp;referrercate=514304</t>
+        </is>
+      </c>
+      <c r="E920" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=886037733445</t>
+        </is>
+      </c>
+      <c r="F920" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D886037733445&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G920" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H920" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="2" t="n">
+        <v>920</v>
+      </c>
+      <c r="B921" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C921" s="2" t="inlineStr">
+        <is>
+          <t>【290Y】【LJ】【854262-001】黑水泥</t>
+        </is>
+      </c>
+      <c r="D921" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065139?uid=1&amp;isSubCate=true&amp;referrercate=514304</t>
+        </is>
+      </c>
+      <c r="E921" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=886384068009</t>
+        </is>
+      </c>
+      <c r="F921" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D886384068009&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G921" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H921" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="2" t="n">
+        <v>921</v>
+      </c>
+      <c r="B922" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C922" s="2" t="inlineStr">
+        <is>
+          <t>【290Y】【LJ】【CT8532-126】AJ3红雀</t>
+        </is>
+      </c>
+      <c r="D922" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065120?uid=1&amp;isSubCate=true&amp;referrercate=514304</t>
+        </is>
+      </c>
+      <c r="E922" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885645406417</t>
+        </is>
+      </c>
+      <c r="F922" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885645406417&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G922" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H922" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" s="2" t="n">
+        <v>922</v>
+      </c>
+      <c r="B923" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C923" s="2" t="inlineStr">
+        <is>
+          <t>【290Y】【LJ】【CT8532-145】白蓝</t>
+        </is>
+      </c>
+      <c r="D923" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065099?uid=1&amp;isSubCate=true&amp;referrercate=514304</t>
+        </is>
+      </c>
+      <c r="E923" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885645518447</t>
+        </is>
+      </c>
+      <c r="F923" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885645518447&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G923" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H923" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" s="2" t="n">
+        <v>923</v>
+      </c>
+      <c r="B924" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C924" s="2" t="inlineStr">
+        <is>
+          <t>【290Y】【LJ】【DA3595-100】AJ3藤原浩</t>
+        </is>
+      </c>
+      <c r="D924" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065081?uid=1&amp;isSubCate=true&amp;referrercate=514304</t>
+        </is>
+      </c>
+      <c r="E924" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885401727223</t>
+        </is>
+      </c>
+      <c r="F924" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885401727223&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G924" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H924" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" s="2" t="n">
+        <v>924</v>
+      </c>
+      <c r="B925" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C925" s="2" t="inlineStr">
+        <is>
+          <t>【290Y】【LJ】【DH3434-110】AJ3 AMM联名米白灰</t>
+        </is>
+      </c>
+      <c r="D925" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065068?uid=1&amp;isSubCate=true&amp;referrercate=514304</t>
+        </is>
+      </c>
+      <c r="E925" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885401787474</t>
+        </is>
+      </c>
+      <c r="F925" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885401787474&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G925" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H925" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="2" t="n">
+        <v>925</v>
+      </c>
+      <c r="B926" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C926" s="2" t="inlineStr">
+        <is>
+          <t>【290Y】【LJ】【DN3707-100】复刻白水泥</t>
+        </is>
+      </c>
+      <c r="D926" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065051?uid=1&amp;isSubCate=true&amp;referrercate=514304</t>
+        </is>
+      </c>
+      <c r="E926" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=886383868147</t>
+        </is>
+      </c>
+      <c r="F926" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D886383868147&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G926" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H926" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="2" t="n">
+        <v>926</v>
+      </c>
+      <c r="B927" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C927" s="2" t="inlineStr">
+        <is>
+          <t>【290Y】【LJ】【FJ9479-100】象牙白</t>
+        </is>
+      </c>
+      <c r="D927" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065038?uid=1&amp;isSubCate=true&amp;referrercate=514304</t>
+        </is>
+      </c>
+      <c r="E927" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=886383828589</t>
+        </is>
+      </c>
+      <c r="F927" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D886383828589&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G927" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H927" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="2" t="n">
+        <v>927</v>
+      </c>
+      <c r="B928" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C928" s="2" t="inlineStr">
+        <is>
+          <t>【370Y】【LJ】【FN0344-901】AJ3 超级腕</t>
+        </is>
+      </c>
+      <c r="D928" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065006?uid=1&amp;isSubCate=true&amp;referrercate=514304</t>
+        </is>
+      </c>
+      <c r="E928" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885644890084</t>
+        </is>
+      </c>
+      <c r="F928" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885644890084&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G928" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H928" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="2" t="n">
+        <v>928</v>
+      </c>
+      <c r="B929" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C929" s="2" t="inlineStr">
+        <is>
+          <t>【370Y】【OWF】【FZ7974-300】AJ3 纽约艺术家联名</t>
+        </is>
+      </c>
+      <c r="D929" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064986?uid=1&amp;isSubCate=true&amp;referrercate=514305</t>
+        </is>
+      </c>
+      <c r="E929" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885645450777</t>
+        </is>
+      </c>
+      <c r="F929" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885645450777&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G929" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H929" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="2" t="n">
+        <v>929</v>
+      </c>
+      <c r="B930" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C930" s="2" t="inlineStr">
+        <is>
+          <t>【I8】 sale Inventory update</t>
+        </is>
+      </c>
+      <c r="D930" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/187085405?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E930" s="2" t="inlineStr">
+        <is>
+          <t>未取得</t>
+        </is>
+      </c>
+      <c r="F930" s="2" t="inlineStr">
+        <is>
+          <t>未取得</t>
+        </is>
+      </c>
+      <c r="G930" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H930" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="2" t="n">
+        <v>930</v>
+      </c>
+      <c r="B931" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C931" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【DA3595-100】藤原浩闪电联名</t>
+        </is>
+      </c>
+      <c r="D931" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065019?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E931" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885111915179</t>
+        </is>
+      </c>
+      <c r="F931" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885111915179&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G931" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H931" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="2" t="n">
+        <v>931</v>
+      </c>
+      <c r="B932" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C932" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【 854262-001】黑水泥</t>
+        </is>
+      </c>
+      <c r="D932" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065887?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E932" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885742633289</t>
+        </is>
+      </c>
+      <c r="F932" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885742633289&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G932" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H932" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="2" t="n">
+        <v>932</v>
+      </c>
+      <c r="B933" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C933" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【 CT8532-008】大象爆裂纹</t>
+        </is>
+      </c>
+      <c r="D933" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065865?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E933" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=886380284858</t>
+        </is>
+      </c>
+      <c r="F933" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D886380284858&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G933" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H933" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="2" t="n">
+        <v>933</v>
+      </c>
+      <c r="B934" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C934" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【 DH3434-113】白棕米</t>
+        </is>
+      </c>
+      <c r="D934" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065846?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E934" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885352226341</t>
+        </is>
+      </c>
+      <c r="F934" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885352226341&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G934" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H934" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="2" t="n">
+        <v>934</v>
+      </c>
+      <c r="B935" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C935" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【 DN3707-160】白红</t>
+        </is>
+      </c>
+      <c r="D935" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065830?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E935" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885110771503</t>
+        </is>
+      </c>
+      <c r="F935" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885110771503&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G935" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H935" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="2" t="n">
+        <v>935</v>
+      </c>
+      <c r="B936" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C936" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【923096-101】球线白水泥</t>
+        </is>
+      </c>
+      <c r="D936" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065820?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E936" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885642650143</t>
+        </is>
+      </c>
+      <c r="F936" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885642650143&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G936" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H936" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="2" t="n">
+        <v>936</v>
+      </c>
+      <c r="B937" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C937" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CJ0939-100】换勾白红</t>
+        </is>
+      </c>
+      <c r="D937" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065808?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E937" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885642170212</t>
+        </is>
+      </c>
+      <c r="F937" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885642170212&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G937" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H937" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="2" t="n">
+        <v>937</v>
+      </c>
+      <c r="B938" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C938" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CK9246-001】奥利奥黑水泥2.0</t>
+        </is>
+      </c>
+      <c r="D938" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065798?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E938" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885641806866</t>
+        </is>
+      </c>
+      <c r="F938" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885641806866&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G938" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H938" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="2" t="n">
+        <v>938</v>
+      </c>
+      <c r="B939" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C939" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CK9246-102】樱花粉</t>
+        </is>
+      </c>
+      <c r="D939" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065781?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E939" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885111771104</t>
+        </is>
+      </c>
+      <c r="F939" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885111771104&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G939" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H939" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="2" t="n">
+        <v>939</v>
+      </c>
+      <c r="B940" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C940" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CK9246-108】湖人白黄</t>
+        </is>
+      </c>
+      <c r="D940" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065770?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E940" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885352570915</t>
+        </is>
+      </c>
+      <c r="F940" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885352570915&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G940" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H940" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="2" t="n">
+        <v>940</v>
+      </c>
+      <c r="B941" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C941" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CK9246-136】幸运绿</t>
+        </is>
+      </c>
+      <c r="D941" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065754?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E941" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885110855500</t>
+        </is>
+      </c>
+      <c r="F941" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885110855500&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G941" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H941" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="2" t="n">
+        <v>941</v>
+      </c>
+      <c r="B942" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C942" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CT8532-031】黑蒂芙尼绿</t>
+        </is>
+      </c>
+      <c r="D942" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065742?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E942" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=886086744636</t>
+        </is>
+      </c>
+      <c r="F942" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D886086744636&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G942" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H942" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="2" t="n">
+        <v>942</v>
+      </c>
+      <c r="B943" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C943" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CT8532-080】恐惧</t>
+        </is>
+      </c>
+      <c r="D943" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065731?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E943" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885743585466</t>
+        </is>
+      </c>
+      <c r="F943" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885743585466&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G943" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H943" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="2" t="n">
+        <v>943</v>
+      </c>
+      <c r="B944" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C944" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CT8532-102】摩卡爆裂纹</t>
+        </is>
+      </c>
+      <c r="D944" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065719?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E944" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885110963911</t>
+        </is>
+      </c>
+      <c r="F944" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885110963911&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G944" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H944" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="2" t="n">
+        <v>944</v>
+      </c>
+      <c r="B945" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C945" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CT8532-104】北卡蓝</t>
+        </is>
+      </c>
+      <c r="D945" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065704?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E945" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885742677806</t>
+        </is>
+      </c>
+      <c r="F945" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885742677806&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G945" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H945" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="2" t="n">
+        <v>945</v>
+      </c>
+      <c r="B946" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C946" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CT8532-105】白紫</t>
+        </is>
+      </c>
+      <c r="D946" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065689?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E946" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885110299645</t>
+        </is>
+      </c>
+      <c r="F946" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885110299645&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G946" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H946" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="2" t="n">
+        <v>946</v>
+      </c>
+      <c r="B947" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C947" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CT8532-106】水泥灰</t>
+        </is>
+      </c>
+      <c r="D947" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065670?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E947" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885110079345</t>
+        </is>
+      </c>
+      <c r="F947" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885110079345&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G947" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H947" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="2" t="n">
+        <v>947</v>
+      </c>
+      <c r="B948" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C948" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CT8532-126】红雀</t>
+        </is>
+      </c>
+      <c r="D948" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065656?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E948" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885743497194</t>
+        </is>
+      </c>
+      <c r="F948" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885743497194&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G948" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H948" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="2" t="n">
+        <v>948</v>
+      </c>
+      <c r="B949" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C949" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CT8532-140】午夜蓝</t>
+        </is>
+      </c>
+      <c r="D949" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065633?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E949" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=886087844573</t>
+        </is>
+      </c>
+      <c r="F949" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D886087844573&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G949" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H949" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="2" t="n">
+        <v>949</v>
+      </c>
+      <c r="B950" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C950" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CT8532-148】奇才白蓝</t>
+        </is>
+      </c>
+      <c r="D950" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065602?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E950" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885353042771</t>
+        </is>
+      </c>
+      <c r="F950" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885353042771&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G950" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H950" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="B951" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C951" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CZ6431-100】火焰红</t>
+        </is>
+      </c>
+      <c r="D951" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065581?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E951" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=886380720545</t>
+        </is>
+      </c>
+      <c r="F951" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D886380720545&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G951" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H951" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="2" t="n">
+        <v>951</v>
+      </c>
+      <c r="B952" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C952" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【DH3434-110】联名白紫灰</t>
+        </is>
+      </c>
+      <c r="D952" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065561?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E952" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=886383040251</t>
+        </is>
+      </c>
+      <c r="F952" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D886383040251&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G952" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H952" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="2" t="n">
+        <v>952</v>
+      </c>
+      <c r="B953" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C953" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【DH7139-100】米白棉布</t>
+        </is>
+      </c>
+      <c r="D953" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065546?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E953" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885742721726</t>
+        </is>
+      </c>
+      <c r="F953" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885742721726&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G953" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H953" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="2" t="n">
+        <v>953</v>
+      </c>
+      <c r="B954" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C954" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【DN3707-100】白水泥</t>
+        </is>
+      </c>
+      <c r="D954" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065531?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E954" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885644330586</t>
+        </is>
+      </c>
+      <c r="F954" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885644330586&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G954" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H954" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="2" t="n">
+        <v>954</v>
+      </c>
+      <c r="B955" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C955" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【FJ9479-100】象牙白</t>
+        </is>
+      </c>
+      <c r="D955" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065512?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E955" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885683670267</t>
+        </is>
+      </c>
+      <c r="F955" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885683670267&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G955" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H955" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="2" t="n">
+        <v>955</v>
+      </c>
+      <c r="B956" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C956" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【FN0344-901】联名白蓝红</t>
+        </is>
+      </c>
+      <c r="D956" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065494?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E956" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885111451377</t>
+        </is>
+      </c>
+      <c r="F956" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885111451377&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G956" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H956" s="2" t="inlineStr">
         <is>
           <t>―</t>
         </is>
@@ -36587,7 +40147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H833"/>
+  <dimension ref="A1:H922"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -69922,6 +73482,3566 @@
         </is>
       </c>
     </row>
+    <row r="834">
+      <c r="A834" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="B834" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C834" s="2" t="inlineStr">
+        <is>
+          <t>【470yuan】【LJR】【DN3707-100】J3 做旧白水泥</t>
+        </is>
+      </c>
+      <c r="D834" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/216704263?uid=1&amp;isSubCate=true&amp;referrercate=514308</t>
+        </is>
+      </c>
+      <c r="E834" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7428248669</t>
+        </is>
+      </c>
+      <c r="F834" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7428248669&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G834" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H834" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" s="2" t="n">
+        <v>834</v>
+      </c>
+      <c r="B835" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C835" s="2" t="inlineStr">
+        <is>
+          <t>【470yuan】【LJR】Air Jordan 3 Retro "Rare Air" 黑灰红 稀有空气</t>
+        </is>
+      </c>
+      <c r="D835" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/207418065?uid=1&amp;isSubCate=true&amp;referrercate=514308</t>
+        </is>
+      </c>
+      <c r="E835" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7428248669</t>
+        </is>
+      </c>
+      <c r="F835" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7428248669&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G835" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H835" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" s="2" t="n">
+        <v>835</v>
+      </c>
+      <c r="B836" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C836" s="2" t="inlineStr">
+        <is>
+          <t>【470Y】【LJR】 CT8532-111 白猫</t>
+        </is>
+      </c>
+      <c r="D836" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/201182629?uid=1&amp;isSubCate=true&amp;referrercate=514308</t>
+        </is>
+      </c>
+      <c r="E836" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7428248669</t>
+        </is>
+      </c>
+      <c r="F836" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7428248669&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G836" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H836" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" s="2" t="n">
+        <v>836</v>
+      </c>
+      <c r="B837" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C837" s="2" t="inlineStr">
+        <is>
+          <t>【470Y】【LJR】【CT8532-101】北卡蓝</t>
+        </is>
+      </c>
+      <c r="D837" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/200243616?uid=1&amp;isSubCate=true&amp;referrercate=514308</t>
+        </is>
+      </c>
+      <c r="E837" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7428248669</t>
+        </is>
+      </c>
+      <c r="F837" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7428248669&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G837" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H837" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" s="2" t="n">
+        <v>837</v>
+      </c>
+      <c r="B838" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C838" s="2" t="inlineStr">
+        <is>
+          <t>【470Y】【LJR】【CT8532-001】AJ3 黑猫</t>
+        </is>
+      </c>
+      <c r="D838" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064139?uid=1&amp;isSubCate=true&amp;referrercate=514308</t>
+        </is>
+      </c>
+      <c r="E838" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7428248669</t>
+        </is>
+      </c>
+      <c r="F838" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7428248669&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G838" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H838" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" s="2" t="n">
+        <v>838</v>
+      </c>
+      <c r="B839" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C839" s="2" t="inlineStr">
+        <is>
+          <t>【470Y】【LJR】【DN3707-010】AJ3奥利奥黑水泥</t>
+        </is>
+      </c>
+      <c r="D839" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064116?uid=1&amp;isSubCate=true&amp;referrercate=514308</t>
+        </is>
+      </c>
+      <c r="E839" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7428248669</t>
+        </is>
+      </c>
+      <c r="F839" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7428248669&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G839" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H839" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" s="2" t="n">
+        <v>839</v>
+      </c>
+      <c r="B840" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C840" s="2" t="inlineStr">
+        <is>
+          <t>【420yuan】【GX】【CT8532-111】AJ3白猫</t>
+        </is>
+      </c>
+      <c r="D840" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/204376714?uid=1&amp;isSubCate=true&amp;referrercate=514298</t>
+        </is>
+      </c>
+      <c r="E840" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7430603222</t>
+        </is>
+      </c>
+      <c r="F840" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7430603222&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G840" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H840" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" s="2" t="n">
+        <v>840</v>
+      </c>
+      <c r="B841" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C841" s="2" t="inlineStr">
+        <is>
+          <t>【420yuan】【GX】AJ3 "Rare Air"稀有空气</t>
+        </is>
+      </c>
+      <c r="D841" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/200880317?uid=1&amp;isSubCate=true&amp;referrercate=514298</t>
+        </is>
+      </c>
+      <c r="E841" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7430603222</t>
+        </is>
+      </c>
+      <c r="F841" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7430603222&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G841" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H841" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" s="2" t="n">
+        <v>841</v>
+      </c>
+      <c r="B842" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C842" s="2" t="inlineStr">
+        <is>
+          <t>【450Y】【GX】【HV8571-100】AJ3 AMM 联名紫 灰蓝</t>
+        </is>
+      </c>
+      <c r="D842" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/189465133?uid=1&amp;isSubCate=true&amp;referrercate=514298</t>
+        </is>
+      </c>
+      <c r="E842" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7430603222</t>
+        </is>
+      </c>
+      <c r="F842" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7430603222&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G842" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H842" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" s="2" t="n">
+        <v>842</v>
+      </c>
+      <c r="B843" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C843" s="2" t="inlineStr">
+        <is>
+          <t>【420Y】【GX】【DA3595-100】AJ3 藤原浩闪电</t>
+        </is>
+      </c>
+      <c r="D843" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/189465043?uid=1&amp;isSubCate=true&amp;referrercate=514298</t>
+        </is>
+      </c>
+      <c r="E843" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7430603222</t>
+        </is>
+      </c>
+      <c r="F843" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7430603222&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G843" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H843" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" s="2" t="n">
+        <v>843</v>
+      </c>
+      <c r="B844" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C844" s="2" t="inlineStr">
+        <is>
+          <t>【420Y】【GX】【DN3707-100】AJ3 做旧白水泥</t>
+        </is>
+      </c>
+      <c r="D844" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/189464807?uid=1&amp;isSubCate=true&amp;referrercate=514298</t>
+        </is>
+      </c>
+      <c r="E844" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7430603222</t>
+        </is>
+      </c>
+      <c r="F844" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7430603222&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G844" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H844" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" s="2" t="n">
+        <v>844</v>
+      </c>
+      <c r="B845" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C845" s="2" t="inlineStr">
+        <is>
+          <t>【420Y】【GX】【CT8532-001】黑猫</t>
+        </is>
+      </c>
+      <c r="D845" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064324?uid=1&amp;isSubCate=true&amp;referrercate=514298</t>
+        </is>
+      </c>
+      <c r="E845" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7430603222</t>
+        </is>
+      </c>
+      <c r="F845" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7430603222&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G845" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H845" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" s="2" t="n">
+        <v>845</v>
+      </c>
+      <c r="B846" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C846" s="2" t="inlineStr">
+        <is>
+          <t>【420Y】【GX】【DN3707-010】 AJ3复刻奥利奥黑水泥</t>
+        </is>
+      </c>
+      <c r="D846" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064299?uid=1&amp;isSubCate=true&amp;referrercate=514298</t>
+        </is>
+      </c>
+      <c r="E846" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7430603222</t>
+        </is>
+      </c>
+      <c r="F846" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7430603222&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G846" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H846" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" s="2" t="n">
+        <v>846</v>
+      </c>
+      <c r="B847" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C847" s="2" t="inlineStr">
+        <is>
+          <t>【410Y】【Y3】【CT8532-001】黑猫</t>
+        </is>
+      </c>
+      <c r="D847" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064390?uid=1&amp;isSubCate=true&amp;referrercate=514300</t>
+        </is>
+      </c>
+      <c r="E847" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7441573607</t>
+        </is>
+      </c>
+      <c r="F847" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7441573607&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G847" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H847" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" s="2" t="n">
+        <v>847</v>
+      </c>
+      <c r="B848" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C848" s="2" t="inlineStr">
+        <is>
+          <t>【410Y】【Y3版】【DN3707-010】 Jordan Air Jordan 3 retro cardinal red</t>
+        </is>
+      </c>
+      <c r="D848" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064352?uid=1&amp;isSubCate=true&amp;referrercate=514300</t>
+        </is>
+      </c>
+      <c r="E848" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7441573607</t>
+        </is>
+      </c>
+      <c r="F848" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7441573607&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G848" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H848" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" s="2" t="n">
+        <v>848</v>
+      </c>
+      <c r="B849" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C849" s="2" t="inlineStr">
+        <is>
+          <t>【390yuan】【RN】IR0912-400 李维斯蓝</t>
+        </is>
+      </c>
+      <c r="D849" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/235416082?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E849" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F849" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G849" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H849" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" s="2" t="n">
+        <v>849</v>
+      </c>
+      <c r="B850" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C850" s="2" t="inlineStr">
+        <is>
+          <t>【390yuan】【RN】854262-106 白蓝</t>
+        </is>
+      </c>
+      <c r="D850" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/229064532?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E850" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F850" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G850" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H850" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" s="2" t="n">
+        <v>850</v>
+      </c>
+      <c r="B851" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C851" s="2" t="inlineStr">
+        <is>
+          <t>【390yuan】【RN】IB1482-100 韩国限定</t>
+        </is>
+      </c>
+      <c r="D851" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/225218809?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E851" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F851" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G851" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H851" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" s="2" t="n">
+        <v>851</v>
+      </c>
+      <c r="B852" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C852" s="2" t="inlineStr">
+        <is>
+          <t>【390yuan】【RN】IF4491-100 迈阿密</t>
+        </is>
+      </c>
+      <c r="D852" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/225173214?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E852" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F852" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G852" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H852" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" s="2" t="n">
+        <v>852</v>
+      </c>
+      <c r="B853" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C853" s="2" t="inlineStr">
+        <is>
+          <t>【390yuan】【RN】HV8571-100 AMM灰蓝</t>
+        </is>
+      </c>
+      <c r="D853" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/214817093?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E853" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F853" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G853" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H853" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" s="2" t="n">
+        <v>853</v>
+      </c>
+      <c r="B854" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C854" s="2" t="inlineStr">
+        <is>
+          <t>【390yuan】【RN】DA3595-100 藤原浩闪电</t>
+        </is>
+      </c>
+      <c r="D854" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/214817037?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E854" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F854" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G854" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H854" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" s="2" t="n">
+        <v>854</v>
+      </c>
+      <c r="B855" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C855" s="2" t="inlineStr">
+        <is>
+          <t>【390yuan】【RN】FJ9479-100 象牙白</t>
+        </is>
+      </c>
+      <c r="D855" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/214816980?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E855" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F855" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G855" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H855" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" s="2" t="n">
+        <v>855</v>
+      </c>
+      <c r="B856" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C856" s="2" t="inlineStr">
+        <is>
+          <t>【390yuan】【RN】【CT8532-104】北卡蓝</t>
+        </is>
+      </c>
+      <c r="D856" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/214816917?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E856" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F856" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G856" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H856" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" s="2" t="n">
+        <v>856</v>
+      </c>
+      <c r="B857" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C857" s="2" t="inlineStr">
+        <is>
+          <t>【390yuan】【RN】DN3707-160 火焰红</t>
+        </is>
+      </c>
+      <c r="D857" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/214262999?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E857" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F857" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G857" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H857" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" s="2" t="n">
+        <v>857</v>
+      </c>
+      <c r="B858" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C858" s="2" t="inlineStr">
+        <is>
+          <t>【390Y】【RN】【DA3595-001】AJ3 反转藤原浩</t>
+        </is>
+      </c>
+      <c r="D858" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/194113227?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E858" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F858" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G858" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H858" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" s="2" t="n">
+        <v>858</v>
+      </c>
+      <c r="B859" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C859" s="2" t="inlineStr">
+        <is>
+          <t>【390Y】【RN】AJ3 白蓝【CT8532-101】</t>
+        </is>
+      </c>
+      <c r="D859" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/192750629?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E859" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F859" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G859" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H859" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" s="2" t="n">
+        <v>859</v>
+      </c>
+      <c r="B860" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C860" s="2" t="inlineStr">
+        <is>
+          <t>【390Y】【RN】复刻白猫 CT8532-111</t>
+        </is>
+      </c>
+      <c r="D860" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/192237796?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E860" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F860" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G860" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H860" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" s="2" t="n">
+        <v>860</v>
+      </c>
+      <c r="B861" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C861" s="2" t="inlineStr">
+        <is>
+          <t>【390Y】【RN】【DH3434-110】AJ3 AMM 联名白</t>
+        </is>
+      </c>
+      <c r="D861" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/191882316?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E861" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F861" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G861" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H861" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" s="2" t="n">
+        <v>861</v>
+      </c>
+      <c r="B862" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C862" s="2" t="inlineStr">
+        <is>
+          <t>【390Y】【RN】【DN3707-010】AJ3 黑水泥</t>
+        </is>
+      </c>
+      <c r="D862" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064466?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E862" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F862" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G862" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H862" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" s="2" t="n">
+        <v>862</v>
+      </c>
+      <c r="B863" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C863" s="2" t="inlineStr">
+        <is>
+          <t>【390Y】【RN】【DN3707-100】J3 做旧白水泥</t>
+        </is>
+      </c>
+      <c r="D863" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064446?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E863" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F863" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G863" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H863" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" s="2" t="n">
+        <v>863</v>
+      </c>
+      <c r="B864" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C864" s="2" t="inlineStr">
+        <is>
+          <t>【390Y】【RN】【FN0344-901】AJ3 白彩虹</t>
+        </is>
+      </c>
+      <c r="D864" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064439?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E864" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F864" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G864" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H864" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" s="2" t="n">
+        <v>864</v>
+      </c>
+      <c r="B865" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C865" s="2" t="inlineStr">
+        <is>
+          <t>【390Y】【RN】【CT8532-001】AJ3 黑猫</t>
+        </is>
+      </c>
+      <c r="D865" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064275?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E865" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F865" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G865" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H865" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" s="2" t="n">
+        <v>865</v>
+      </c>
+      <c r="B866" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C866" s="2" t="inlineStr">
+        <is>
+          <t>【390Y】【RN】【FN0344-001】AJ3 黑彩虹</t>
+        </is>
+      </c>
+      <c r="D866" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064255?uid=1&amp;isSubCate=true&amp;referrercate=514307</t>
+        </is>
+      </c>
+      <c r="E866" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7445542880</t>
+        </is>
+      </c>
+      <c r="F866" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7445542880&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G866" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H866" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" s="2" t="n">
+        <v>866</v>
+      </c>
+      <c r="B867" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C867" s="2" t="inlineStr">
+        <is>
+          <t>【400yuan】【OG】 CK9246-100 米银</t>
+        </is>
+      </c>
+      <c r="D867" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/223349677?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E867" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F867" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G867" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H867" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" s="2" t="n">
+        <v>867</v>
+      </c>
+      <c r="B868" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C868" s="2" t="inlineStr">
+        <is>
+          <t>【400Y】【OG】【IB8967-004】AJ3 黑蓝</t>
+        </is>
+      </c>
+      <c r="D868" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/194127379?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E868" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F868" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G868" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H868" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" s="2" t="n">
+        <v>868</v>
+      </c>
+      <c r="B869" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C869" s="2" t="inlineStr">
+        <is>
+          <t>【450Y】【OG】【DN3707-010 】奥利奥黑水泥</t>
+        </is>
+      </c>
+      <c r="D869" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064172?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E869" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F869" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G869" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H869" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" s="2" t="n">
+        <v>869</v>
+      </c>
+      <c r="B870" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C870" s="2" t="inlineStr">
+        <is>
+          <t>【450Y】【OG】【FZ7974-300】Nina Chanel Abney x Air Jordan 3 Retro AJ3 乔3纽约艺术家联名</t>
+        </is>
+      </c>
+      <c r="D870" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064155?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E870" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F870" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G870" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H870" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" s="2" t="n">
+        <v>870</v>
+      </c>
+      <c r="B871" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C871" s="2" t="inlineStr">
+        <is>
+          <t>【440Y】【OG】 【FN0344-001】APJ Balvin x Air Jordan AJ3</t>
+        </is>
+      </c>
+      <c r="D871" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064219?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E871" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F871" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G871" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H871" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" s="2" t="n">
+        <v>871</v>
+      </c>
+      <c r="B872" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C872" s="2" t="inlineStr">
+        <is>
+          <t>【440Y】【OG】【FN0344-901】APJ Balvin x Air Jordan AJ3</t>
+        </is>
+      </c>
+      <c r="D872" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064202?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E872" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F872" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G872" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H872" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" s="2" t="n">
+        <v>872</v>
+      </c>
+      <c r="B873" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C873" s="2" t="inlineStr">
+        <is>
+          <t>【400Y】【OG】【 DN3707-100】 Jordan Air Jordan 3 White Cement Reimagined</t>
+        </is>
+      </c>
+      <c r="D873" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064624?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E873" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F873" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G873" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H873" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" s="2" t="n">
+        <v>873</v>
+      </c>
+      <c r="B874" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C874" s="2" t="inlineStr">
+        <is>
+          <t>【400Y】【OG】【CT8532-102】 Jordan Air Jordan 3白黑摩卡</t>
+        </is>
+      </c>
+      <c r="D874" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064610?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E874" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F874" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G874" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H874" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" s="2" t="n">
+        <v>874</v>
+      </c>
+      <c r="B875" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C875" s="2" t="inlineStr">
+        <is>
+          <t>【400Y】【OG】【CT8532-126】 Jordan Air Jordan 3 retro cardinal red</t>
+        </is>
+      </c>
+      <c r="D875" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064597?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E875" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F875" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G875" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H875" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" s="2" t="n">
+        <v>875</v>
+      </c>
+      <c r="B876" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C876" s="2" t="inlineStr">
+        <is>
+          <t>【400Y】【OG】【DA3595-100】 Fragment Design x Jordan Air Jordan 3 retro sp white</t>
+        </is>
+      </c>
+      <c r="D876" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064581?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E876" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F876" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G876" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H876" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" s="2" t="n">
+        <v>876</v>
+      </c>
+      <c r="B877" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C877" s="2" t="inlineStr">
+        <is>
+          <t>【400Y】【OG】【DH3434-110】4 a aniere x Jordan Air Jordan 3 retro sp mediumgrey”</t>
+        </is>
+      </c>
+      <c r="D877" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064563?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E877" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F877" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G877" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H877" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" s="2" t="n">
+        <v>877</v>
+      </c>
+      <c r="B878" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C878" s="2" t="inlineStr">
+        <is>
+          <t>【400Y】【OG】【FJ9479-100】AJ3 灰白爆裂</t>
+        </is>
+      </c>
+      <c r="D878" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064545?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E878" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F878" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G878" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H878" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" s="2" t="n">
+        <v>878</v>
+      </c>
+      <c r="B879" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C879" s="2" t="inlineStr">
+        <is>
+          <t>【400Y】【OG】【HJ0178-600】粉色</t>
+        </is>
+      </c>
+      <c r="D879" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064512?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E879" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F879" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G879" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H879" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" s="2" t="n">
+        <v>879</v>
+      </c>
+      <c r="B880" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C880" s="2" t="inlineStr">
+        <is>
+          <t>【 400 】 【 OG 】 【 CT8532-140 】 AJ3 Midnight Blue!</t>
+        </is>
+      </c>
+      <c r="D880" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185066068?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E880" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F880" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G880" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H880" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" s="2" t="n">
+        <v>880</v>
+      </c>
+      <c r="B881" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C881" s="2" t="inlineStr">
+        <is>
+          <t>【 400 】 【OG】 【 854262 001】AJ3 black cement!</t>
+        </is>
+      </c>
+      <c r="D881" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185066055?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E881" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F881" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G881" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H881" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" s="2" t="n">
+        <v>881</v>
+      </c>
+      <c r="B882" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C882" s="2" t="inlineStr">
+        <is>
+          <t>【 400 】 【OG】 【CK9246-001  】 Oreo Black Cement!</t>
+        </is>
+      </c>
+      <c r="D882" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185066032?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E882" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F882" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G882" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H882" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" s="2" t="n">
+        <v>882</v>
+      </c>
+      <c r="B883" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C883" s="2" t="inlineStr">
+        <is>
+          <t>【 400 】 【OG】 【CT8532-104】 AJ3 North Carolina Blue!</t>
+        </is>
+      </c>
+      <c r="D883" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185066017?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E883" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F883" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G883" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H883" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" s="2" t="n">
+        <v>883</v>
+      </c>
+      <c r="B884" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C884" s="2" t="inlineStr">
+        <is>
+          <t>【 400 】 【OG】 【CT8532-145】AJ3 Racing Blue!</t>
+        </is>
+      </c>
+      <c r="D884" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065997?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E884" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F884" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G884" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H884" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" s="2" t="n">
+        <v>884</v>
+      </c>
+      <c r="B885" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C885" s="2" t="inlineStr">
+        <is>
+          <t>【 450 】 【 OG 】 【 FZ4811-001 】 AJ3AMM Joint Black Purple!</t>
+        </is>
+      </c>
+      <c r="D885" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065956?uid=1&amp;isSubCate=true&amp;referrercate=514296</t>
+        </is>
+      </c>
+      <c r="E885" s="2" t="inlineStr">
+        <is>
+          <t>https://weidian.com/item.html?itemID=7429179595</t>
+        </is>
+      </c>
+      <c r="F885" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fweidian.com%2Fitem.html%3FitemID%3D7429179595&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G885" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H885" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" s="2" t="n">
+        <v>885</v>
+      </c>
+      <c r="B886" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C886" s="2" t="inlineStr">
+        <is>
+          <t>【290Y】【LJ】【 CT8532-148】奇才蓝</t>
+        </is>
+      </c>
+      <c r="D886" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065154?uid=1&amp;isSubCate=true&amp;referrercate=514304</t>
+        </is>
+      </c>
+      <c r="E886" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=886037733445</t>
+        </is>
+      </c>
+      <c r="F886" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D886037733445&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G886" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H886" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" s="2" t="n">
+        <v>886</v>
+      </c>
+      <c r="B887" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C887" s="2" t="inlineStr">
+        <is>
+          <t>【290Y】【LJ】【854262-001】黑水泥</t>
+        </is>
+      </c>
+      <c r="D887" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065139?uid=1&amp;isSubCate=true&amp;referrercate=514304</t>
+        </is>
+      </c>
+      <c r="E887" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=886384068009</t>
+        </is>
+      </c>
+      <c r="F887" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D886384068009&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G887" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H887" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" s="2" t="n">
+        <v>887</v>
+      </c>
+      <c r="B888" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C888" s="2" t="inlineStr">
+        <is>
+          <t>【290Y】【LJ】【CT8532-126】AJ3红雀</t>
+        </is>
+      </c>
+      <c r="D888" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065120?uid=1&amp;isSubCate=true&amp;referrercate=514304</t>
+        </is>
+      </c>
+      <c r="E888" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885645406417</t>
+        </is>
+      </c>
+      <c r="F888" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885645406417&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G888" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H888" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" s="2" t="n">
+        <v>888</v>
+      </c>
+      <c r="B889" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C889" s="2" t="inlineStr">
+        <is>
+          <t>【290Y】【LJ】【CT8532-145】白蓝</t>
+        </is>
+      </c>
+      <c r="D889" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065099?uid=1&amp;isSubCate=true&amp;referrercate=514304</t>
+        </is>
+      </c>
+      <c r="E889" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885645518447</t>
+        </is>
+      </c>
+      <c r="F889" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885645518447&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G889" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H889" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" s="2" t="n">
+        <v>889</v>
+      </c>
+      <c r="B890" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C890" s="2" t="inlineStr">
+        <is>
+          <t>【290Y】【LJ】【DA3595-100】AJ3藤原浩</t>
+        </is>
+      </c>
+      <c r="D890" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065081?uid=1&amp;isSubCate=true&amp;referrercate=514304</t>
+        </is>
+      </c>
+      <c r="E890" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885401727223</t>
+        </is>
+      </c>
+      <c r="F890" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885401727223&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G890" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H890" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" s="2" t="n">
+        <v>890</v>
+      </c>
+      <c r="B891" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C891" s="2" t="inlineStr">
+        <is>
+          <t>【290Y】【LJ】【DH3434-110】AJ3 AMM联名米白灰</t>
+        </is>
+      </c>
+      <c r="D891" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065068?uid=1&amp;isSubCate=true&amp;referrercate=514304</t>
+        </is>
+      </c>
+      <c r="E891" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885401787474</t>
+        </is>
+      </c>
+      <c r="F891" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885401787474&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G891" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H891" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" s="2" t="n">
+        <v>891</v>
+      </c>
+      <c r="B892" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C892" s="2" t="inlineStr">
+        <is>
+          <t>【290Y】【LJ】【DN3707-100】复刻白水泥</t>
+        </is>
+      </c>
+      <c r="D892" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065051?uid=1&amp;isSubCate=true&amp;referrercate=514304</t>
+        </is>
+      </c>
+      <c r="E892" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=886383868147</t>
+        </is>
+      </c>
+      <c r="F892" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D886383868147&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G892" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H892" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" s="2" t="n">
+        <v>892</v>
+      </c>
+      <c r="B893" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C893" s="2" t="inlineStr">
+        <is>
+          <t>【290Y】【LJ】【FJ9479-100】象牙白</t>
+        </is>
+      </c>
+      <c r="D893" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065038?uid=1&amp;isSubCate=true&amp;referrercate=514304</t>
+        </is>
+      </c>
+      <c r="E893" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=886383828589</t>
+        </is>
+      </c>
+      <c r="F893" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D886383828589&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G893" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H893" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" s="2" t="n">
+        <v>893</v>
+      </c>
+      <c r="B894" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C894" s="2" t="inlineStr">
+        <is>
+          <t>【370Y】【LJ】【FN0344-901】AJ3 超级腕</t>
+        </is>
+      </c>
+      <c r="D894" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065006?uid=1&amp;isSubCate=true&amp;referrercate=514304</t>
+        </is>
+      </c>
+      <c r="E894" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885644890084</t>
+        </is>
+      </c>
+      <c r="F894" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885644890084&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G894" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H894" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" s="2" t="n">
+        <v>894</v>
+      </c>
+      <c r="B895" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C895" s="2" t="inlineStr">
+        <is>
+          <t>【370Y】【OWF】【FZ7974-300】AJ3 纽约艺术家联名</t>
+        </is>
+      </c>
+      <c r="D895" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185064986?uid=1&amp;isSubCate=true&amp;referrercate=514305</t>
+        </is>
+      </c>
+      <c r="E895" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885645450777</t>
+        </is>
+      </c>
+      <c r="F895" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885645450777&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G895" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H895" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" s="2" t="n">
+        <v>895</v>
+      </c>
+      <c r="B896" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C896" s="2" t="inlineStr">
+        <is>
+          <t>【I8】 sale Inventory update</t>
+        </is>
+      </c>
+      <c r="D896" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/187085405?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E896" s="2" t="inlineStr">
+        <is>
+          <t>未取得</t>
+        </is>
+      </c>
+      <c r="F896" s="2" t="inlineStr">
+        <is>
+          <t>未取得</t>
+        </is>
+      </c>
+      <c r="G896" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H896" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" s="2" t="n">
+        <v>896</v>
+      </c>
+      <c r="B897" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C897" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【DA3595-100】藤原浩闪电联名</t>
+        </is>
+      </c>
+      <c r="D897" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065019?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E897" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885111915179</t>
+        </is>
+      </c>
+      <c r="F897" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885111915179&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G897" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H897" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" s="2" t="n">
+        <v>897</v>
+      </c>
+      <c r="B898" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C898" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【 854262-001】黑水泥</t>
+        </is>
+      </c>
+      <c r="D898" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065887?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E898" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885742633289</t>
+        </is>
+      </c>
+      <c r="F898" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885742633289&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G898" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H898" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="B899" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C899" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【 CT8532-008】大象爆裂纹</t>
+        </is>
+      </c>
+      <c r="D899" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065865?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E899" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=886380284858</t>
+        </is>
+      </c>
+      <c r="F899" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D886380284858&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G899" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H899" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" s="2" t="n">
+        <v>899</v>
+      </c>
+      <c r="B900" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C900" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【 DH3434-113】白棕米</t>
+        </is>
+      </c>
+      <c r="D900" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065846?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E900" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885352226341</t>
+        </is>
+      </c>
+      <c r="F900" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885352226341&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G900" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H900" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" s="2" t="n">
+        <v>900</v>
+      </c>
+      <c r="B901" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C901" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【 DN3707-160】白红</t>
+        </is>
+      </c>
+      <c r="D901" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065830?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E901" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885110771503</t>
+        </is>
+      </c>
+      <c r="F901" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885110771503&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G901" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H901" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" s="2" t="n">
+        <v>901</v>
+      </c>
+      <c r="B902" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C902" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【923096-101】球线白水泥</t>
+        </is>
+      </c>
+      <c r="D902" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065820?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E902" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885642650143</t>
+        </is>
+      </c>
+      <c r="F902" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885642650143&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G902" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H902" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" s="2" t="n">
+        <v>902</v>
+      </c>
+      <c r="B903" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C903" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CJ0939-100】换勾白红</t>
+        </is>
+      </c>
+      <c r="D903" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065808?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E903" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885642170212</t>
+        </is>
+      </c>
+      <c r="F903" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885642170212&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G903" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H903" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" s="2" t="n">
+        <v>903</v>
+      </c>
+      <c r="B904" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C904" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CK9246-001】奥利奥黑水泥2.0</t>
+        </is>
+      </c>
+      <c r="D904" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065798?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E904" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885641806866</t>
+        </is>
+      </c>
+      <c r="F904" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885641806866&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G904" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H904" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" s="2" t="n">
+        <v>904</v>
+      </c>
+      <c r="B905" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C905" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CK9246-102】樱花粉</t>
+        </is>
+      </c>
+      <c r="D905" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065781?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E905" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885111771104</t>
+        </is>
+      </c>
+      <c r="F905" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885111771104&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G905" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H905" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" s="2" t="n">
+        <v>905</v>
+      </c>
+      <c r="B906" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C906" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CK9246-108】湖人白黄</t>
+        </is>
+      </c>
+      <c r="D906" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065770?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E906" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885352570915</t>
+        </is>
+      </c>
+      <c r="F906" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885352570915&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G906" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H906" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" s="2" t="n">
+        <v>906</v>
+      </c>
+      <c r="B907" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C907" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CK9246-136】幸运绿</t>
+        </is>
+      </c>
+      <c r="D907" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065754?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E907" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885110855500</t>
+        </is>
+      </c>
+      <c r="F907" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885110855500&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G907" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H907" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" s="2" t="n">
+        <v>907</v>
+      </c>
+      <c r="B908" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C908" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CT8532-031】黑蒂芙尼绿</t>
+        </is>
+      </c>
+      <c r="D908" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065742?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E908" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=886086744636</t>
+        </is>
+      </c>
+      <c r="F908" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D886086744636&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G908" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H908" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" s="2" t="n">
+        <v>908</v>
+      </c>
+      <c r="B909" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C909" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CT8532-080】恐惧</t>
+        </is>
+      </c>
+      <c r="D909" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065731?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E909" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885743585466</t>
+        </is>
+      </c>
+      <c r="F909" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885743585466&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G909" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H909" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" s="2" t="n">
+        <v>909</v>
+      </c>
+      <c r="B910" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C910" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CT8532-102】摩卡爆裂纹</t>
+        </is>
+      </c>
+      <c r="D910" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065719?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E910" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885110963911</t>
+        </is>
+      </c>
+      <c r="F910" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885110963911&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G910" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H910" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" s="2" t="n">
+        <v>910</v>
+      </c>
+      <c r="B911" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C911" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CT8532-104】北卡蓝</t>
+        </is>
+      </c>
+      <c r="D911" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065704?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E911" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885742677806</t>
+        </is>
+      </c>
+      <c r="F911" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885742677806&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G911" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H911" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" s="2" t="n">
+        <v>911</v>
+      </c>
+      <c r="B912" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C912" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CT8532-105】白紫</t>
+        </is>
+      </c>
+      <c r="D912" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065689?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E912" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885110299645</t>
+        </is>
+      </c>
+      <c r="F912" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885110299645&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G912" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H912" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" s="2" t="n">
+        <v>912</v>
+      </c>
+      <c r="B913" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C913" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CT8532-106】水泥灰</t>
+        </is>
+      </c>
+      <c r="D913" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065670?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E913" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885110079345</t>
+        </is>
+      </c>
+      <c r="F913" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885110079345&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G913" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H913" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" s="2" t="n">
+        <v>913</v>
+      </c>
+      <c r="B914" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C914" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CT8532-126】红雀</t>
+        </is>
+      </c>
+      <c r="D914" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065656?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E914" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885743497194</t>
+        </is>
+      </c>
+      <c r="F914" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885743497194&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G914" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H914" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" s="2" t="n">
+        <v>914</v>
+      </c>
+      <c r="B915" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C915" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CT8532-140】午夜蓝</t>
+        </is>
+      </c>
+      <c r="D915" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065633?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E915" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=886087844573</t>
+        </is>
+      </c>
+      <c r="F915" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D886087844573&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G915" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H915" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" s="2" t="n">
+        <v>915</v>
+      </c>
+      <c r="B916" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C916" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CT8532-148】奇才白蓝</t>
+        </is>
+      </c>
+      <c r="D916" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065602?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E916" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885353042771</t>
+        </is>
+      </c>
+      <c r="F916" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885353042771&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G916" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H916" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" s="2" t="n">
+        <v>916</v>
+      </c>
+      <c r="B917" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C917" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【CZ6431-100】火焰红</t>
+        </is>
+      </c>
+      <c r="D917" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065581?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E917" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=886380720545</t>
+        </is>
+      </c>
+      <c r="F917" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D886380720545&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G917" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H917" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" s="2" t="n">
+        <v>917</v>
+      </c>
+      <c r="B918" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C918" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【DH3434-110】联名白紫灰</t>
+        </is>
+      </c>
+      <c r="D918" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065561?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E918" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=886383040251</t>
+        </is>
+      </c>
+      <c r="F918" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D886383040251&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G918" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H918" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" s="2" t="n">
+        <v>918</v>
+      </c>
+      <c r="B919" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C919" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【DH7139-100】米白棉布</t>
+        </is>
+      </c>
+      <c r="D919" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065546?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E919" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885742721726</t>
+        </is>
+      </c>
+      <c r="F919" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885742721726&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G919" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H919" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" s="2" t="n">
+        <v>919</v>
+      </c>
+      <c r="B920" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C920" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【DN3707-100】白水泥</t>
+        </is>
+      </c>
+      <c r="D920" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065531?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E920" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885644330586</t>
+        </is>
+      </c>
+      <c r="F920" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885644330586&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G920" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H920" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" s="2" t="n">
+        <v>920</v>
+      </c>
+      <c r="B921" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C921" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【FJ9479-100】象牙白</t>
+        </is>
+      </c>
+      <c r="D921" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065512?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E921" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885683670267</t>
+        </is>
+      </c>
+      <c r="F921" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885683670267&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G921" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H921" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" s="2" t="n">
+        <v>921</v>
+      </c>
+      <c r="B922" s="2" t="inlineStr">
+        <is>
+          <t>SNEAKERS</t>
+        </is>
+      </c>
+      <c r="C922" s="2" t="inlineStr">
+        <is>
+          <t>【155】【I8】【FN0344-901】联名白蓝红</t>
+        </is>
+      </c>
+      <c r="D922" s="2" t="inlineStr">
+        <is>
+          <t>https://repsmaster.x.yupoo.com/albums/185065494?uid=1&amp;isSubCate=true&amp;referrercate=514302</t>
+        </is>
+      </c>
+      <c r="E922" s="2" t="inlineStr">
+        <is>
+          <t>https://item.taobao.com/item.htm?ft=t&amp;id=885111451377</t>
+        </is>
+      </c>
+      <c r="F922" s="2" t="inlineStr">
+        <is>
+          <t>https://www.kakobuy.com/item/details?url=https%3A%2F%2Fitem.taobao.com%2Fitem.htm%3Fft%3Dt%26id%3D885111451377&amp;affcode=a235412</t>
+        </is>
+      </c>
+      <c r="G922" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+      <c r="H922" s="2" t="inlineStr">
+        <is>
+          <t>―</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
